--- a/templates/excel/oot-readiness.xlsx
+++ b/templates/excel/oot-readiness.xlsx
@@ -10,8 +10,8 @@
     <sheet name="Questions" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Scoring" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Recommendations" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="README" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="_metadata" sheetId="5" state="hidden" r:id="rId5"/>
+    <sheet name="_metadata" sheetId="4" state="hidden" r:id="rId4"/>
+    <sheet name="README" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -73,7 +73,7 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00FFC7CE"/>
+          <fgColor rgb="00C6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -87,7 +87,7 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00C6EFCE"/>
+          <fgColor rgb="00FFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1129,15 +1129,15 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="D6">
-    <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="0">
-      <formula>0.60</formula>
+    <cfRule type="cellIs" priority="1" operator="greaterThanOrEqual" dxfId="0">
+      <formula>0.75</formula>
     </cfRule>
     <cfRule type="cellIs" priority="2" operator="between" dxfId="1">
       <formula>0.60</formula>
-      <formula>0.75</formula>
+      <formula>0.7499</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="greaterThanOrEqual" dxfId="2">
-      <formula>0.75</formula>
+    <cfRule type="cellIs" priority="3" operator="lessThan" dxfId="2">
+      <formula>0.60</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1228,153 +1228,66 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A24"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="110" customWidth="1" min="1" max="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t># oot-readiness.xlsx</t>
+          <t>key</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>value</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>spec_version</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>1.0.0</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>PURPOSE</t>
+          <t>generation_date</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20-question pre-adoption diagnostic across People / Tech / Culture / Risk dimensions. Run once before adopting ØØT.</t>
+          <t>oot_version</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>1.0.0</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>INTERPRETATION</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>- Total ≥75% (≥30/40): green light. Adopt.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>- Total 60–75% (24-29/40): yellow. Address gaps in lowest-scoring dimension first.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>- Total &lt;60% (&lt;24/40): red. Adoption is premature. The framework's discipline applies to the framework itself: don't push past genuine readiness gaps.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>WRITTEN BY</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>- The founder, once at adoption.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>- Re-run quarterly during Year 1 to track readiness evolution; annually thereafter.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>REVIEWED BY</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>- Founder.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>- Recommended: read the recommendations sheet alongside the score; address weakest dimension first.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>DO NOT</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>- Score yourself optimistically. The discipline of the framework starts with the readiness assessment.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>- Skip questions. Each question maps to a real adoption risk.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>- Adopt below 60% without written documentation of how the gaps will be addressed in the first 90 days.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>This is a diagnostic, not a gate. Founders may proceed below 60% with documented mitigation, but the framework's authors recommend honestly addressing gaps before sunk-cost dynamics make later course correction harder.</t>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>file_id</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>X9</t>
         </is>
       </c>
     </row>
@@ -1389,66 +1302,153 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:A24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="110" customWidth="1" min="1" max="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>key</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>value</t>
+          <t># oot-readiness.xlsx</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>spec_version</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>1.0.0</t>
-        </is>
-      </c>
+      <c r="A2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>generation_date</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
+          <t>PURPOSE</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>oot_version</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>1.0.0</t>
+          <t>20-question pre-adoption diagnostic across People / Tech / Culture / Risk dimensions. Run once before adopting ØØT.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>file_id</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>X9</t>
+      <c r="A5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>INTERPRETATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>- Total ≥75% (≥30/40): green light. Adopt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>- Total 60–75% (24-29/40): yellow. Address gaps in lowest-scoring dimension first.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>- Total &lt;60% (&lt;24/40): red. Adoption is premature. The framework's discipline applies to the framework itself: don't push past genuine readiness gaps.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>WRITTEN BY</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>- The founder, once at adoption.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>- Re-run quarterly during Year 1 to track readiness evolution; annually thereafter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>REVIEWED BY</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>- Founder.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>- Recommended: read the recommendations sheet alongside the score; address weakest dimension first.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>DO NOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>- Score yourself optimistically. The discipline of the framework starts with the readiness assessment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>- Skip questions. Each question maps to a real adoption risk.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>- Adopt below 60% without written documentation of how the gaps will be addressed in the first 90 days.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>This is a diagnostic, not a gate. Founders may proceed below 60% with documented mitigation, but the framework's authors recommend honestly addressing gaps before sunk-cost dynamics make later course correction harder.</t>
         </is>
       </c>
     </row>
